--- a/Persona1 y Persona2.xlsx
+++ b/Persona1 y Persona2.xlsx
@@ -17,7 +17,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="3">
+  <fonts count="4">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -27,6 +27,11 @@
     </font>
     <font>
       <b val="1"/>
+    </font>
+    <font>
+      <name val="Times New Roman"/>
+      <b val="1"/>
+      <sz val="11"/>
     </font>
     <font>
       <name val="Times New Roman"/>
@@ -67,7 +72,7 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -474,7 +479,7 @@
       </c>
       <c r="D2" s="3" t="inlineStr">
         <is>
-          <t>https://sneex17.github.io/?Persona1=Margot&amp;Persona2=Janovis&amp;Cantidad=2</t>
+          <t>https://dayanyrashell.netlify.app/?Persona1=Margot&amp;Persona2=Janovis&amp;Cantidad=2</t>
         </is>
       </c>
     </row>
@@ -494,7 +499,7 @@
       </c>
       <c r="D3" s="3" t="inlineStr">
         <is>
-          <t>https://sneex17.github.io/?Persona1=Mairelis&amp;Persona2=Mar%C3%ADa&amp;Cantidad=3</t>
+          <t>https://dayanyrashell.netlify.app/?Persona1=Mairelis&amp;Persona2=Mar%C3%ADa&amp;Cantidad=3</t>
         </is>
       </c>
     </row>
@@ -514,7 +519,7 @@
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t>https://sneex17.github.io/?Persona1=Euclides&amp;Persona2=Mar%C3%ADa%20Luisa&amp;Cantidad=2</t>
+          <t>https://dayanyrashell.netlify.app/?Persona1=Euclides&amp;Persona2=Mar%C3%ADa%20Luisa&amp;Cantidad=2</t>
         </is>
       </c>
     </row>
